--- a/dinofluxdata.xlsx
+++ b/dinofluxdata.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/y_f_bats_uu_nl/Documents/Documents/PhD/FluxModel/Rebuttal PP/GitHub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{6D5CFAD4-E290-4359-B333-6CA6CECF30C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC46F4BF-2F59-49AC-A45F-678360222FF4}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{6D5CFAD4-E290-4359-B333-6CA6CECF30C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB691744-9BB4-49D2-BF5B-77D27A915C01}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A1315DA-632D-4DC5-A574-5C40FA3B0F05}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3A1315DA-632D-4DC5-A574-5C40FA3B0F05}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Units" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="16">
   <si>
     <t>Species</t>
   </si>
@@ -78,13 +79,19 @@
   </si>
   <si>
     <t>doi</t>
+  </si>
+  <si>
+    <t>μmol/kg</t>
+  </si>
+  <si>
+    <t>unitless fraction</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +112,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -138,6 +151,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -876,4 +890,39 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA688A7-0017-444E-9042-B8353C171103}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>